--- a/src/staticfiles/study/templates/crf_template_fields_import_template.xlsx
+++ b/src/staticfiles/study/templates/crf_template_fields_import_template.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,41 @@
           <t>Comments En</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Review Study Version</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Review Type</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Review Required For Verify</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Review Required For Lock</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Review Blocking If Missing</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Review Role Required</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Review Enabled</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
